--- a/dist/downloads/model-documents/openbmb-minicpm-sala.xlsx
+++ b/dist/downloads/model-documents/openbmb-minicpm-sala.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R376f8ecc4aca40e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R8615ca19655d4e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="Rf402c8fc71104969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R1e998e7f70854f3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1061,7 +1061,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -8145,7 +8145,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD83" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="24" hidden="0" customHeight="1">
@@ -13757,7 +13757,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD144" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="24" hidden="0" customHeight="1">
@@ -14953,7 +14953,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD157" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="24" hidden="0" customHeight="1">
@@ -19093,7 +19093,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD202" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="24" hidden="0" customHeight="1">
@@ -24705,7 +24705,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD263" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="24" hidden="0" customHeight="1">
@@ -25901,7 +25901,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD276" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="24" hidden="0" customHeight="1">
@@ -27097,7 +27097,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD289" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="24" hidden="0" customHeight="1">
@@ -28083,7 +28083,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -28347,7 +28347,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -28360,7 +28363,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -29184,8 +29190,8 @@
       <x:c r="E86" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -29193,6 +29199,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
